--- a/prova_real/trimestre_09/resultado_T9.xlsx
+++ b/prova_real/trimestre_09/resultado_T9.xlsx
@@ -576,17 +576,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ISAE4</t>
+          <t>EMBJ3</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -598,10 +598,10 @@
         <v>56.5</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>7.65</v>
+        <v>11.06</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>3.89</v>
+        <v>62.69</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -624,22 +624,22 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1</v>
+        <v>7.78</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>4.69</v>
+        <v>23.53</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>-2.3238</v>
+        <v>-3.7633</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>972.5</v>
+        <v>12538</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>25972.5</v>
+        <v>32538</v>
       </c>
     </row>
     <row r="3">
@@ -650,17 +650,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>CURY3</t>
+          <t>CAML3</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -672,10 +672,10 @@
         <v>54.8</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>6.53</v>
+        <v>5.77</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>1.62</v>
+        <v>15.92</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1.11</v>
+        <v>0.36</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>7.09</v>
+        <v>4.38</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>-3.6136</v>
+        <v>0.1098</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>405</v>
+        <v>3184</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>25405</v>
+        <v>23184</v>
       </c>
     </row>
     <row r="4">
@@ -724,17 +724,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>PETR4</t>
+          <t>CSMG3</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -746,10 +746,10 @@
         <v>54.8</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>13.62</v>
+        <v>11.88</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>-5.43</v>
+        <v>6.91</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
@@ -758,12 +758,12 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2.97</v>
+        <v>0.91</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>10.62</v>
+        <v>5.26</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>-2.1239</v>
+        <v>-1.3346</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-1357.5</v>
+        <v>1382</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>23642.5</v>
+        <v>21382</v>
       </c>
     </row>
     <row r="5">
@@ -798,17 +798,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>PCAR3</t>
+          <t>ISAE4</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>64.5</v>
+        <v>58.1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>1622.23</v>
+        <v>7.89</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>-24.12</v>
+        <v>3.75</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
@@ -832,110 +832,110 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>✅ COMPRAR</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>-2.3273</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>750</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>20750</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>T-9</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>PETR4</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-27</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Previsibilidade Moderada</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>-6.83</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>❌ NÃO</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>✅ COMPRAR</t>
         </is>
       </c>
-      <c r="M5" s="2" t="n">
-        <v>6.49</v>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>214.75</v>
-      </c>
-      <c r="O5" s="2" t="n">
-        <v>-256.5771</v>
-      </c>
-      <c r="P5" s="2" t="n">
-        <v>25000</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>-6030</v>
-      </c>
-      <c r="R5" s="2" t="n">
-        <v>18970</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>T-9</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>MBRF3</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>2024-02-22</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>2024-05-22</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Pouco Previsível</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>13.37</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>33.22</v>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ OBSERVAR</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>5.01</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>0.0917</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0</v>
+      <c r="M6" s="2" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>-2.7357</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>-1366</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>18634</v>
       </c>
     </row>
     <row r="7">
@@ -946,17 +946,17 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>DMVF3</t>
+          <t>CXSE3</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -968,10 +968,10 @@
         <v>53.2</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>10.56</v>
+        <v>13.98</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>29.74</v>
+        <v>11.6</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.66</v>
+        <v>0.74</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>8.970000000000001</v>
+        <v>5.62</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.2652</v>
+        <v>-1.6438</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>0</v>
@@ -1020,17 +1020,17 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>CAML3</t>
+          <t>CEAB3</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1042,10 +1042,10 @@
         <v>53.2</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>5.87</v>
+        <v>16.41</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>10.87</v>
+        <v>7.86</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0.33</v>
+        <v>1.39</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>4.04</v>
+        <v>13.9</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>0.08890000000000001</v>
+        <v>-2.1565</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>0</v>
@@ -1094,17 +1094,17 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>CXSE3</t>
+          <t>CURY3</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1116,10 +1116,10 @@
         <v>53.2</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>13.71</v>
+        <v>7.02</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>10.28</v>
+        <v>4.76</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
@@ -1142,13 +1142,13 @@
         </is>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0.86</v>
+        <v>0.98</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>6.51</v>
+        <v>6.24</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-1.8201</v>
+        <v>-2.898</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>0</v>
@@ -1168,17 +1168,17 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>CEAB3</t>
+          <t>POMO4</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1190,10 +1190,10 @@
         <v>53.2</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>16.07</v>
+        <v>15.51</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>9.67</v>
+        <v>3.21</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
@@ -1216,13 +1216,13 @@
         </is>
       </c>
       <c r="M10" s="3" t="n">
-        <v>1.48</v>
+        <v>0.38</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>14.96</v>
+        <v>7.22</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>-2.1222</v>
+        <v>-3.4565</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0</v>
@@ -1242,17 +1242,17 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>POMO4</t>
+          <t>BBAS3</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1264,10 +1264,10 @@
         <v>53.2</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>15.25</v>
+        <v>10.57</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>8.01</v>
+        <v>-5.82</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
@@ -1276,183 +1276,183 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>❌ NÃO</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>⚠️ OBSERVAR</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>-22.3119</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>T-9</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>ALUP11</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-27</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Muito Previsível</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
           <t>ALTA</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ OBSERVAR</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="N11" s="3" t="n">
-        <v>7.51</v>
-      </c>
-      <c r="O11" s="3" t="n">
-        <v>-3.027</v>
-      </c>
-      <c r="P11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>T-9</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>CSMG3</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>2024-02-22</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>2024-05-22</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Pouco Previsível</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>11.28</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO INDICADO</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="O12" s="4" t="n">
+        <v>-0.0343</v>
+      </c>
+      <c r="P12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>T-9</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>KEPL3</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-27</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Muito Previsível</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>-1.86</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ OBSERVAR</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="N12" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O12" s="3" t="n">
-        <v>-0.66</v>
-      </c>
-      <c r="P12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>T-9</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>BBAS3</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>2024-02-22</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>2024-05-22</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Pouco Previsível</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>-4.65</v>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>❌ NÃO</t>
         </is>
       </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ OBSERVAR</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="N13" s="3" t="n">
-        <v>7.39</v>
-      </c>
-      <c r="O13" s="3" t="n">
-        <v>-19.9437</v>
-      </c>
-      <c r="P13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="3" t="n">
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO INDICADO</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="N13" s="4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O13" s="4" t="n">
+        <v>-0.8563</v>
+      </c>
+      <c r="P13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1464,41 +1464,41 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>EGIE3</t>
+          <t>LOGN3</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Pouco Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>53.2</v>
+        <v>56.5</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.27</v>
+        <v>-9.56</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>11.02</v>
+        <v>-1.91</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
@@ -1512,13 +1512,13 @@
         </is>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.12</v>
+        <v>2.63</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>4.25</v>
+        <v>6.76</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.1102</v>
+        <v>-2.3448</v>
       </c>
       <c r="P14" s="4" t="n">
         <v>0</v>
@@ -1538,32 +1538,32 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>ALUP11</t>
+          <t>AURE3</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>61.3</v>
+        <v>53.2</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.26</v>
+        <v>3.33</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>7.58</v>
+        <v>-2.89</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1586,13 +1586,13 @@
         </is>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.5</v>
+        <v>1.14</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.93</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.0399</v>
+        <v>-22.0082</v>
       </c>
       <c r="P15" s="4" t="n">
         <v>0</v>
@@ -1612,17 +1612,17 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>KEPL3</t>
+          <t>SMTO3</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -1634,10 +1634,10 @@
         <v>56.5</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.84</v>
+        <v>-17.23</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>4.86</v>
+        <v>-3.7</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
@@ -1646,12 +1646,12 @@
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
@@ -1660,13 +1660,13 @@
         </is>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.22</v>
+        <v>3.25</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>2.52</v>
+        <v>12.12</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.1528</v>
+        <v>-8.4977</v>
       </c>
       <c r="P16" s="4" t="n">
         <v>0</v>
@@ -1686,17 +1686,17 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>LOGN3</t>
+          <t>PRIO3</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -1708,10 +1708,10 @@
         <v>54.8</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-9.68</v>
+        <v>-2.37</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>3.47</v>
+        <v>-3.81</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
@@ -1720,12 +1720,12 @@
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1734,13 +1734,13 @@
         </is>
       </c>
       <c r="M17" s="4" t="n">
-        <v>2.53</v>
+        <v>3.2</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>6.49</v>
+        <v>6.61</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.0964</v>
+        <v>-2.1975</v>
       </c>
       <c r="P17" s="4" t="n">
         <v>0</v>
@@ -1760,17 +1760,17 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>SMTO3</t>
+          <t>BRKM5</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1782,10 +1782,10 @@
         <v>54.8</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-15.67</v>
+        <v>-15.06</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.38</v>
+        <v>-9.33</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
@@ -1808,13 +1808,13 @@
         </is>
       </c>
       <c r="M18" s="4" t="n">
-        <v>2.73</v>
+        <v>6.46</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>10.13</v>
+        <v>28.26</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-5.9905</v>
+        <v>-6.4272</v>
       </c>
       <c r="P18" s="4" t="n">
         <v>0</v>
@@ -1834,41 +1834,41 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>ENEV3</t>
+          <t>PNVL3</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Pouco Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>53.2</v>
+        <v>59.7</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.84</v>
+        <v>-1.4</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.37</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
@@ -1882,13 +1882,13 @@
         </is>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.25</v>
+        <v>0.45</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.05</v>
+        <v>4.31</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.0494</v>
+        <v>0.0325</v>
       </c>
       <c r="P19" s="4" t="n">
         <v>0</v>
@@ -1908,32 +1908,32 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>LAND3</t>
+          <t>ONCO3</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F20" s="4" t="n">
-        <v>54.8</v>
+        <v>53.2</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-36.12</v>
+        <v>-1.25</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-2.5</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
@@ -1956,13 +1956,13 @@
         </is>
       </c>
       <c r="M20" s="4" t="n">
-        <v>4.34</v>
+        <v>2.52</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>28.15</v>
+        <v>33.63</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-10.3004</v>
+        <v>-3.1666</v>
       </c>
       <c r="P20" s="4" t="n">
         <v>0</v>
@@ -1982,17 +1982,17 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>VAMO3</t>
+          <t>FIQE3</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -2001,13 +2001,13 @@
         </is>
       </c>
       <c r="F21" s="4" t="n">
-        <v>56.5</v>
+        <v>58.1</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-17.08</v>
+        <v>-0.98</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-5.15</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
@@ -2030,13 +2030,13 @@
         </is>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.84</v>
+        <v>0.18</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>11.12</v>
+        <v>6.12</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-2.6359</v>
+        <v>-1.1341</v>
       </c>
       <c r="P21" s="4" t="n">
         <v>0</v>
@@ -2056,17 +2056,17 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>PRIO3</t>
+          <t>LAND3</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -2075,13 +2075,13 @@
         </is>
       </c>
       <c r="F22" s="4" t="n">
-        <v>56.5</v>
+        <v>58.1</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.17</v>
+        <v>-35.79</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-5.84</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
@@ -2104,13 +2104,13 @@
         </is>
       </c>
       <c r="M22" s="4" t="n">
-        <v>3.19</v>
+        <v>4.35</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>6.59</v>
+        <v>28.26</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.569</v>
+        <v>-10.2613</v>
       </c>
       <c r="P22" s="4" t="n">
         <v>0</v>
@@ -2130,32 +2130,32 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>FIQE3</t>
+          <t>JALL3</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F23" s="4" t="n">
-        <v>58.1</v>
+        <v>54.8</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.59</v>
+        <v>-5.37</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-9.58</v>
+        <v>-10.46</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
@@ -2178,13 +2178,13 @@
         </is>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>7.34</v>
+        <v>2.78</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.9044</v>
+        <v>0.4733</v>
       </c>
       <c r="P23" s="4" t="n">
         <v>0</v>
@@ -2204,17 +2204,17 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>PNVL3</t>
+          <t>VAMO3</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -2223,13 +2223,13 @@
         </is>
       </c>
       <c r="F24" s="4" t="n">
-        <v>58.1</v>
+        <v>56.5</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.6</v>
+        <v>-16.45</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-9.77</v>
+        <v>-11.11</v>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
@@ -2252,13 +2252,13 @@
         </is>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.41</v>
+        <v>0.8</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.86</v>
+        <v>10.5</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.0985</v>
+        <v>-2.5639</v>
       </c>
       <c r="P24" s="4" t="n">
         <v>0</v>
@@ -2278,17 +2278,17 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>ROMI3</t>
+          <t>HYPE3</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -2300,10 +2300,10 @@
         <v>54.8</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.43</v>
+        <v>-13.8</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-9.93</v>
+        <v>-11.17</v>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
@@ -2326,13 +2326,13 @@
         </is>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.59</v>
+        <v>2.71</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>6.16</v>
+        <v>9.4</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.0702</v>
+        <v>-1.9678</v>
       </c>
       <c r="P25" s="4" t="n">
         <v>0</v>
@@ -2352,17 +2352,17 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>HYPE3</t>
+          <t>RAIL3</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -2371,13 +2371,13 @@
         </is>
       </c>
       <c r="F26" s="4" t="n">
-        <v>56.5</v>
+        <v>62.9</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-14.75</v>
+        <v>-0.18</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-9.99</v>
+        <v>-11.48</v>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
@@ -2400,13 +2400,13 @@
         </is>
       </c>
       <c r="M26" s="4" t="n">
-        <v>3.07</v>
+        <v>1.1</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>10.64</v>
+        <v>5.52</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.6125</v>
+        <v>-1.8909</v>
       </c>
       <c r="P26" s="4" t="n">
         <v>0</v>
@@ -2426,32 +2426,32 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>RAIL3</t>
+          <t>ROMI3</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F27" s="4" t="n">
-        <v>62.9</v>
+        <v>53.2</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.22</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-10.07</v>
+        <v>-12.6</v>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.99</v>
+        <v>0.64</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>4.95</v>
+        <v>6.7</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.5099</v>
+        <v>-0.0297</v>
       </c>
       <c r="P27" s="4" t="n">
         <v>0</v>
@@ -2505,12 +2505,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="F28" s="4" t="n">
-        <v>56.5</v>
+        <v>58.1</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-11.24</v>
+        <v>-10.28</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-10.5</v>
+        <v>-15.31</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
@@ -2548,13 +2548,13 @@
         </is>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>12.69</v>
+        <v>11.15</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-8.4236</v>
+        <v>-4.75</v>
       </c>
       <c r="P28" s="4" t="n">
         <v>0</v>
@@ -2574,32 +2574,32 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>JALL3</t>
+          <t>BLAU3</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>54.8</v>
+        <v>53.2</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-4.85</v>
+        <v>-23.25</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-10.55</v>
+        <v>-15.33</v>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.21</v>
+        <v>0.33</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>2.91</v>
+        <v>4.27</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.3697</v>
+        <v>0.4008</v>
       </c>
       <c r="P29" s="4" t="n">
         <v>0</v>
@@ -2648,32 +2648,32 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>NEXP3</t>
+          <t>FESA4</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Pouco Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F30" s="4" t="n">
-        <v>53.2</v>
+        <v>61.3</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-19.08</v>
+        <v>-6.58</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-12.63</v>
+        <v>-15.45</v>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
@@ -2696,13 +2696,13 @@
         </is>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.32</v>
+        <v>1.28</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>7.31</v>
+        <v>17.85</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-1.5216</v>
+        <v>-8.737299999999999</v>
       </c>
       <c r="P30" s="4" t="n">
         <v>0</v>
@@ -2722,17 +2722,17 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>MDIA3</t>
+          <t>UNIP6</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -2741,13 +2741,13 @@
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>58.1</v>
+        <v>61.3</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-3.57</v>
+        <v>-5.74</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-13.52</v>
+        <v>-15.65</v>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
@@ -2770,13 +2770,13 @@
         </is>
       </c>
       <c r="M31" s="4" t="n">
-        <v>2.24</v>
+        <v>2.87</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>6.1</v>
+        <v>6.92</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.2181</v>
+        <v>-0.5282</v>
       </c>
       <c r="P31" s="4" t="n">
         <v>0</v>
@@ -2796,32 +2796,32 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>RENT3</t>
+          <t>LREN3</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F32" s="4" t="n">
-        <v>62.9</v>
+        <v>53.2</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-5.77</v>
+        <v>-1.96</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-13.78</v>
+        <v>-16.6</v>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
@@ -2844,13 +2844,13 @@
         </is>
       </c>
       <c r="M32" s="4" t="n">
-        <v>2.14</v>
+        <v>0.97</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>4.72</v>
+        <v>7.4</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.5058</v>
+        <v>-1.0561</v>
       </c>
       <c r="P32" s="4" t="n">
         <v>0</v>
@@ -2870,17 +2870,17 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>FESA4</t>
+          <t>RENT3</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -2889,13 +2889,13 @@
         </is>
       </c>
       <c r="F33" s="4" t="n">
-        <v>61.3</v>
+        <v>64.5</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-5.93</v>
+        <v>-5.44</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-15.48</v>
+        <v>-16.94</v>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="M33" s="4" t="n">
-        <v>1.34</v>
+        <v>2.42</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>18.69</v>
+        <v>5.43</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-7.923</v>
+        <v>-0.5669</v>
       </c>
       <c r="P33" s="4" t="n">
         <v>0</v>
@@ -2944,32 +2944,32 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>BLAU3</t>
+          <t>TASA4</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F34" s="4" t="n">
-        <v>54.8</v>
+        <v>64.5</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-22.7</v>
+        <v>-2.71</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-16.26</v>
+        <v>-18.34</v>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
@@ -2992,13 +2992,13 @@
         </is>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.3</v>
+        <v>1.28</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>3.82</v>
+        <v>12.08</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.5142</v>
+        <v>-2.2147</v>
       </c>
       <c r="P34" s="4" t="n">
         <v>0</v>
@@ -3018,17 +3018,17 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>UNIP6</t>
+          <t>MDIA3</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -3037,13 +3037,13 @@
         </is>
       </c>
       <c r="F35" s="4" t="n">
-        <v>61.3</v>
+        <v>59.7</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-5.27</v>
+        <v>-2.3</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-17.79</v>
+        <v>-18.58</v>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
@@ -3066,13 +3066,13 @@
         </is>
       </c>
       <c r="M35" s="4" t="n">
-        <v>2.95</v>
+        <v>2.16</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>7.03</v>
+        <v>6.03</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.7451</v>
+        <v>0.0477</v>
       </c>
       <c r="P35" s="4" t="n">
         <v>0</v>
@@ -3092,17 +3092,17 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>TASA4</t>
+          <t>PCAR3</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
@@ -3111,13 +3111,13 @@
         </is>
       </c>
       <c r="F36" s="4" t="n">
-        <v>66.09999999999999</v>
+        <v>61.3</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>-2.2</v>
+        <v>-42056.28</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>-18.95</v>
+        <v>-21.32</v>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
@@ -3140,13 +3140,13 @@
         </is>
       </c>
       <c r="M36" s="4" t="n">
-        <v>1.29</v>
+        <v>5.75</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>12.07</v>
+        <v>191.35</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>-2.3208</v>
+        <v>-233.8052</v>
       </c>
       <c r="P36" s="4" t="n">
         <v>0</v>
@@ -3166,32 +3166,32 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>SIMH3</t>
+          <t>EZTC3</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>62.9</v>
+        <v>53.2</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>-11.7</v>
+        <v>-21.67</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>-19.84</v>
+        <v>-23.59</v>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
@@ -3214,13 +3214,13 @@
         </is>
       </c>
       <c r="M37" s="4" t="n">
-        <v>0.91</v>
+        <v>1.39</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>7.19</v>
+        <v>13.56</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>0.362</v>
+        <v>-1.64</v>
       </c>
       <c r="P37" s="4" t="n">
         <v>0</v>
@@ -3240,17 +3240,17 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>CSAN3</t>
+          <t>COCE5</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -3262,10 +3262,10 @@
         <v>61.3</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-0.21</v>
+        <v>-8.58</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>-22.48</v>
+        <v>-23.87</v>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
@@ -3288,13 +3288,13 @@
         </is>
       </c>
       <c r="M38" s="4" t="n">
-        <v>2.37</v>
+        <v>1.93</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>16.36</v>
+        <v>6.08</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>-4.4566</v>
+        <v>0.1027</v>
       </c>
       <c r="P38" s="4" t="n">
         <v>0</v>
@@ -3314,17 +3314,17 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>MOVI3</t>
+          <t>COGN3</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -3336,10 +3336,10 @@
         <v>54.8</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>-13.12</v>
+        <v>-2.35</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>-23.96</v>
+        <v>-23.92</v>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="M39" s="4" t="n">
-        <v>0.79</v>
+        <v>0.45</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>11.89</v>
+        <v>24.3</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>-0.7211</v>
+        <v>-4.1317</v>
       </c>
       <c r="P39" s="4" t="n">
         <v>0</v>
@@ -3388,32 +3388,32 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>LWSA3</t>
+          <t>SIMH3</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>54.8</v>
+        <v>64.5</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>-14.32</v>
+        <v>-12.31</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>-25.18</v>
+        <v>-24.6</v>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M40" s="4" t="n">
-        <v>0.32</v>
+        <v>0.93</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>6.21</v>
+        <v>7.29</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>0.1979</v>
+        <v>0.3974</v>
       </c>
       <c r="P40" s="4" t="n">
         <v>0</v>
@@ -3462,32 +3462,32 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>ONCO3</t>
+          <t>LWSA3</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Pouco Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>53.2</v>
+        <v>54.8</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>-0.33</v>
+        <v>-14.27</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>-26.75</v>
+        <v>-25.8</v>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
@@ -3510,13 +3510,13 @@
         </is>
       </c>
       <c r="M41" s="4" t="n">
-        <v>2.66</v>
+        <v>0.32</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>35.39</v>
+        <v>6.49</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>-3.4055</v>
+        <v>0.3463</v>
       </c>
       <c r="P41" s="4" t="n">
         <v>0</v>
@@ -3536,32 +3536,32 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>COCE5</t>
+          <t>MOVI3</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>61.3</v>
+        <v>53.2</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>-10.21</v>
+        <v>-15.23</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>-28.26</v>
+        <v>-26.09</v>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
@@ -3584,13 +3584,13 @@
         </is>
       </c>
       <c r="M42" s="4" t="n">
-        <v>1.61</v>
+        <v>0.62</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>4.8</v>
+        <v>9.5</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>0.4242</v>
+        <v>0.0565</v>
       </c>
       <c r="P42" s="4" t="n">
         <v>0</v>
@@ -3610,32 +3610,32 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>YDUQ3</t>
+          <t>QUAL3</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Pouco Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>53.2</v>
+        <v>56.5</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>-2.11</v>
+        <v>-30.78</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>-28.52</v>
+        <v>-30.29</v>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
@@ -3658,13 +3658,13 @@
         </is>
       </c>
       <c r="M43" s="4" t="n">
-        <v>2.67</v>
+        <v>0.2</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>19.41</v>
+        <v>11.29</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>-0.8688</v>
+        <v>0.5538</v>
       </c>
       <c r="P43" s="4" t="n">
         <v>0</v>
@@ -3689,12 +3689,12 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -3706,10 +3706,10 @@
         <v>54.8</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>-18.85</v>
+        <v>-18.65</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>-28.91</v>
+        <v>-30.42</v>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="M44" s="4" t="n">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>10.03</v>
+        <v>11.06</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>0.4102</v>
+        <v>0.2857</v>
       </c>
       <c r="P44" s="4" t="n">
         <v>0</v>
@@ -3758,17 +3758,17 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>MGLU3</t>
+          <t>YDUQ3</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -3777,13 +3777,13 @@
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>58.1</v>
+        <v>56.5</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>-24.01</v>
+        <v>-2.29</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>-30.33</v>
+        <v>-35.54</v>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
@@ -3806,13 +3806,13 @@
         </is>
       </c>
       <c r="M45" s="4" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>17.15</v>
+        <v>21.1</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>-1.0084</v>
+        <v>-1.0013</v>
       </c>
       <c r="P45" s="4" t="n">
         <v>0</v>
@@ -3832,17 +3832,17 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>QUAL3</t>
+          <t>MGLU3</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
@@ -3851,13 +3851,13 @@
         </is>
       </c>
       <c r="F46" s="4" t="n">
-        <v>59.7</v>
+        <v>61.3</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>-31.96</v>
+        <v>-21.62</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>-33.47</v>
+        <v>-40.23</v>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
@@ -3880,13 +3880,13 @@
         </is>
       </c>
       <c r="M46" s="4" t="n">
-        <v>0.19</v>
+        <v>2.21</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>10.39</v>
+        <v>12.99</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>0.612</v>
+        <v>-0.3077</v>
       </c>
       <c r="P46" s="4" t="n">
         <v>0</v>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -3925,13 +3925,13 @@
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>62.9</v>
+        <v>59.7</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>-31.24</v>
+        <v>-33.58</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>-53.66</v>
+        <v>-41.26</v>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
@@ -3954,13 +3954,13 @@
         </is>
       </c>
       <c r="M47" s="4" t="n">
-        <v>0.99</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>21.86</v>
+        <v>20.63</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>0.4236</v>
+        <v>0.5147</v>
       </c>
       <c r="P47" s="4" t="n">
         <v>0</v>
@@ -3983,7 +3983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4000,7 +4000,7 @@
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
     <col width="17" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
     <col width="20" customWidth="1" min="18" max="18"/>
@@ -4106,17 +4106,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ISAE4</t>
+          <t>EMBJ3</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -4128,10 +4128,10 @@
         <v>56.5</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>7.65</v>
+        <v>11.06</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>3.89</v>
+        <v>62.69</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -4154,22 +4154,22 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1</v>
+        <v>7.78</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>4.69</v>
+        <v>23.53</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>-2.3238</v>
+        <v>-3.7633</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>972.5</v>
+        <v>12538</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>25972.5</v>
+        <v>32538</v>
       </c>
     </row>
     <row r="3">
@@ -4180,17 +4180,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>CURY3</t>
+          <t>CAML3</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -4202,10 +4202,10 @@
         <v>54.8</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>6.53</v>
+        <v>5.77</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>1.62</v>
+        <v>15.92</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -4228,22 +4228,22 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1.11</v>
+        <v>0.36</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>7.09</v>
+        <v>4.38</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>-3.6136</v>
+        <v>0.1098</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>405</v>
+        <v>3184</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>25405</v>
+        <v>23184</v>
       </c>
     </row>
     <row r="4">
@@ -4254,17 +4254,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>PETR4</t>
+          <t>CSMG3</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -4276,10 +4276,10 @@
         <v>54.8</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>13.62</v>
+        <v>11.88</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>-5.43</v>
+        <v>6.91</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
@@ -4288,12 +4288,12 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -4302,22 +4302,22 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2.97</v>
+        <v>0.91</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>10.62</v>
+        <v>5.26</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>-2.1239</v>
+        <v>-1.3346</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-1357.5</v>
+        <v>1382</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>23642.5</v>
+        <v>21382</v>
       </c>
     </row>
     <row r="5">
@@ -4328,17 +4328,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>PCAR3</t>
+          <t>ISAE4</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>64.5</v>
+        <v>58.1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>1622.23</v>
+        <v>7.89</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>-24.12</v>
+        <v>3.75</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
@@ -4362,36 +4362,110 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>✅ COMPRAR</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>-2.3273</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>750</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>20750</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>T-9</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>PETR4</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-27</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Previsibilidade Moderada</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>-6.83</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>❌ NÃO</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>✅ COMPRAR</t>
         </is>
       </c>
-      <c r="M5" s="2" t="n">
-        <v>6.49</v>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>214.75</v>
-      </c>
-      <c r="O5" s="2" t="n">
-        <v>-256.5771</v>
-      </c>
-      <c r="P5" s="2" t="n">
-        <v>25000</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>-6030</v>
-      </c>
-      <c r="R5" s="2" t="n">
-        <v>18970</v>
+      <c r="M6" s="2" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>-2.7357</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>-1366</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>18634</v>
       </c>
     </row>
   </sheetData>
